--- a/data/trans_bre/P16A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,25</t>
+          <t>-2,01; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,04</t>
+          <t>-2,58; 3,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,73</t>
+          <t>-3,48; 1,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,35</t>
+          <t>-2,86; 1,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,96; 156,24</t>
+          <t>-50,89; 168,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 194,36</t>
+          <t>-60,57; 170,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 62,92</t>
+          <t>-65,64; 79,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,61; 57,56</t>
+          <t>-58,08; 53,73</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,95</t>
+          <t>0,24; 5,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,53</t>
+          <t>-1,68; 4,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,31</t>
+          <t>-1,87; 4,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,45</t>
+          <t>0,39; 5,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 671,96</t>
+          <t>-20,55; 895,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 209,97</t>
+          <t>-35,21; 198,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 257,45</t>
+          <t>-45,72; 248,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 268,07</t>
+          <t>6,69; 247,5</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 6,29</t>
+          <t>-0,68; 6,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,47</t>
+          <t>0,94; 9,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 11,24</t>
+          <t>2,16; 11,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 12,3</t>
+          <t>2,49; 12,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 347,31</t>
+          <t>-26,41; 364,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 252,4</t>
+          <t>8,74; 247,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,91; 511,32</t>
+          <t>49,31; 558,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,75; 715,73</t>
+          <t>33,52; 806,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,49</t>
+          <t>0,67; 4,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,98</t>
+          <t>1,65; 6,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,58</t>
+          <t>1,66; 6,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,27</t>
+          <t>-1,46; 4,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 221,63</t>
+          <t>20,03; 214,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,26; 250,04</t>
+          <t>40,57; 250,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,3; 218,62</t>
+          <t>37,17; 212,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 106,1</t>
+          <t>-29,88; 107,67</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,71</t>
+          <t>-0,1; 5,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,3</t>
+          <t>3,24; 8,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,03</t>
+          <t>4,54; 10,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 7,45</t>
+          <t>0,45; 7,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 219,5</t>
+          <t>-5,19; 208,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,27; 463,79</t>
+          <t>67,26; 427,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,19; 311,97</t>
+          <t>79,83; 321,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 151,97</t>
+          <t>4,78; 158,05</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,77</t>
+          <t>1,53; 5,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,09</t>
+          <t>3,13; 8,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,86</t>
+          <t>3,4; 7,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,91</t>
+          <t>4,51; 10,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,2; 1236,51</t>
+          <t>26,28; 957,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,49; 2226,09</t>
+          <t>57,14; 1932,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,57; 1022,03</t>
+          <t>90,47; 1022,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78,27; 825,42</t>
+          <t>70,2; 858,74</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,63</t>
+          <t>1,74; 3,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,99</t>
+          <t>2,68; 4,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,27</t>
+          <t>2,92; 5,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,25</t>
+          <t>2,26; 5,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,7; 165,24</t>
+          <t>55,13; 162,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,42; 175,23</t>
+          <t>70,7; 177,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,05; 174,15</t>
+          <t>72,8; 168,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>52,02; 156,64</t>
+          <t>51,59; 157,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,85%</t>
+          <t>-10,78%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,53</t>
+          <t>-2,06; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,01</t>
+          <t>-2,43; 3,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,98</t>
+          <t>-3,45; 1,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,23</t>
+          <t>-2,35; 1,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 168,1</t>
+          <t>-52,68; 180,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 170,79</t>
+          <t>-57,82; 165,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-65,64; 79,02</t>
+          <t>-66,25; 63,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,08; 53,73</t>
+          <t>-55,62; 56,67</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>103,28%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,25</t>
+          <t>0,29; 4,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 4,94</t>
+          <t>-2,08; 5,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,25</t>
+          <t>-1,83; 3,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,32</t>
+          <t>0,83; 5,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 895,11</t>
+          <t>-25,99; 698,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 198,16</t>
+          <t>-40,73; 213,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 248,09</t>
+          <t>-46,03; 238,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 247,5</t>
+          <t>12,43; 296,02</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>161,33%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,33</t>
+          <t>-0,8; 6,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,54</t>
+          <t>1,07; 9,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,63</t>
+          <t>2,08; 11,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 12,63</t>
+          <t>0,78; 9,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 364,39</t>
+          <t>-35,98; 337,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 247,68</t>
+          <t>16,31; 273,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,31; 558,06</t>
+          <t>42,95; 560,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,52; 806,67</t>
+          <t>9,16; 218,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,42</t>
+          <t>0,89; 4,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,07</t>
+          <t>1,68; 6,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,36</t>
+          <t>1,82; 6,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,27</t>
+          <t>1,57; 5,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,03; 214,28</t>
+          <t>24,07; 229,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,57; 250,82</t>
+          <t>41,92; 252,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,17; 212,81</t>
+          <t>35,5; 204,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 107,67</t>
+          <t>27,35; 151,6</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,48</t>
+          <t>0,07; 5,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,19</t>
+          <t>3,49; 8,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,15</t>
+          <t>4,39; 10,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 7,48</t>
+          <t>2,66; 7,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 208,33</t>
+          <t>-3,69; 241,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,26; 427,6</t>
+          <t>79,54; 481,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,83; 321,77</t>
+          <t>77,05; 333,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 158,05</t>
+          <t>31,79; 189,18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>284,76%</t>
+          <t>268,96%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,7</t>
+          <t>1,76; 5,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,05</t>
+          <t>3,22; 8,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,66</t>
+          <t>3,47; 7,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,15</t>
+          <t>4,05; 9,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,28; 957,49</t>
+          <t>40,09; 1354,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57,14; 1932,55</t>
+          <t>53,99; 2216,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,47; 1022,42</t>
+          <t>83,58; 1111,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70,2; 858,74</t>
+          <t>54,09; 727,83</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,64</t>
+          <t>1,77; 3,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,93</t>
+          <t>2,8; 5,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,19</t>
+          <t>3,01; 5,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,26</t>
+          <t>3,06; 5,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,13; 162,42</t>
+          <t>60,52; 166,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,7; 177,02</t>
+          <t>70,34; 179,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,8; 168,43</t>
+          <t>73,39; 171,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,59; 157,24</t>
+          <t>62,84; 131,03</t>
         </is>
       </c>
     </row>
